--- a/10-financiero/evaluacion-economica-pizzeria-v3.xlsx
+++ b/10-financiero/evaluacion-economica-pizzeria-v3.xlsx
@@ -22,7 +22,11 @@
     <sheet name="Monte_Carlo" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Tasa_Descuento" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="Estructura_Capital" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="Auditoria" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Estado_Resultados" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Capital_Trabajo" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Ratios" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="Respuestas" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Auditoria" sheetId="19" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Escenarios!$4:$4</definedName>
@@ -135,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="595">
   <si>
     <t xml:space="preserve">EVALUACIÓN ECONÓMICA — PIZZERÍA B2B</t>
   </si>
@@ -1289,7 +1293,7 @@
     <t xml:space="preserve">Estado de esta hoja</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculado el 2026-08-06 08:15 sobre VAN base -91,764,381 CLP.</t>
+    <t xml:space="preserve">Calculado el 2026-08-06 18:18 sobre VAN base -91,764,381 CLP.</t>
   </si>
   <si>
     <t xml:space="preserve">Bajo</t>
@@ -1646,6 +1650,231 @@
     <t xml:space="preserve">Brecha a cubrir con planta propia contra el techo de $30.000.000: $95.493.563. Ningún crédito de consumo de este tamaño la cierra.</t>
   </si>
   <si>
+    <t xml:space="preserve">ESTADO DE RESULTADOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por año, con margen de contribución y porcentaje sobre ingresos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% ingresos año 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volumen (unidades)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen de contribución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultado neto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPITAL DE TRABAJO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días de cobro, inventario y pago, y por qué un modelo anual subestima el peak.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuentas por cobrar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuentas por pagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital de trabajo neto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variación del período</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicadores de ciclo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSO · días de cobro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIO · días de inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPO · días de pago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciclo de conversión de caja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADVERTENCIA. Este modelo es anual y no tiene perfil mensual de caja, así que el fondeo máximo que reporta IGNORA el valle intra-anual. Con DPO en cero se supone además que ningún proveedor da crédito, supuesto conservador que nadie ha verificado. La etapa 11 publicó un ratio peak/valle de 2,1 para pernoctaciones INE, pero es un proxy turístico y no una serie de demanda de pizza: usarlo como índice de estacionalidad sería inventar. El perfil mensual queda pendiente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATIOS Y ECONOMÍA UNITARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por qué el proyecto no cierra, en indicadores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio neto por pizza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año 1, con escalador de inflación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo variable por pizza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insumos con merma, envase, energía y distribución.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen de contribución por pizza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo que deja cada pizza para pagar costos fijos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen de contribución %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sobre precio de venta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo fijo mensual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arriendo, personal y gastos de estructura.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidades que igualan contribución y costo fijo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacidad instalada mensual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etapa 04, desde la geometría del abatidor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por sobre 100% el equilibrio es inalcanzable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apalancamiento operativo (DOL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No definido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución total sobre EBITDA; no definido con EBITDA negativo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margen de seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No definido: la operación no alcanza el equilibrio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAN por peso de fondeo máximo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Índice correcto bajo racionamiento de capital: el denominador es la caja que hay que poner, no la inversión inicial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criterio &gt; 1. Usa la inversión inicial como denominador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAS SEIS PREGUNTAS DEL STATEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respuesta actual de cada una, la etapa responsable y qué falta para cerrarla.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pregunta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respuesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qué falta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuántos establecimientos HORECA hay y cuánto consumen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.187 en Temuco y 1.588 en el anillo 1. El consumo por establecimiento sigue sin medir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 · 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrevistas en terreno con el instrumento de la etapa 03.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿A qué precio compran hoy y cuánto pagarían por la alternativa local?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de retail y foodservice levantadas. La disposición a pagar no está medida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 · 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prueba monádica de tres precios, etapa 03.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuál es el CAPEX mínimo con cotizaciones reales?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$29.684.013 con precios de publicación. Cinco de las ocho líneas heredadas no resistieron la auditoría.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 · 07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotizaciones formales; el escenario de equipo usado no pudo construirse por ausencia de mercado publicado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuánto capital de trabajo exige el ciclo de cobro?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7.263.577 inicial, con plazo de cobro supuesto de 30 días.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plazo de cobro real por segmento, y un perfil mensual que capture el valle intra-anual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cuál es el punto de equilibrio y qué porcentaje de la capacidad representa?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.170 pizzas/mes contra una capacidad de 1.320/mes: 164% de la capacidad instalada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04 · 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medir el ciclo real de abatimiento con sonda al centro térmico; los 240 min son un techo prestado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cabe en $50 millones? Si no, ¿cuál es el mínimo real y qué caminos existen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No con planta propia: exige $125.493.563 de fondeo. Sí por maquila, mientras la tarifa no supere $810/pizza ($560 si el techo es $30 millones).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 · 12 · 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotizar la maquila. Es el único camino que cabe en el capital disponible.</t>
+  </si>
+  <si>
     <t xml:space="preserve">AUDITORÍA DE LA CONSTRUCCIÓN</t>
   </si>
   <si>
@@ -1691,7 +1920,7 @@
     <t xml:space="preserve">Generado</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-06 08:15</t>
+    <t xml:space="preserve">2026-08-06 18:18</t>
   </si>
   <si>
     <t xml:space="preserve">TIR calculable</t>
@@ -2396,7 +2625,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="142">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2917,6 +3146,50 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="33" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="31" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="9" xfId="38" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="7" xfId="37" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="9" xfId="37" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="12" xfId="37" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="2" xfId="41" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="33" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="8" xfId="41" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="6" borderId="2" xfId="46" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="10" xfId="41" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="26" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3200,7 +3473,7 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFE8F3EC"/>
       <rgbColor rgb="FF7E0021"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF579D1C"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF9A6700"/>
       <rgbColor rgb="FF800080"/>
@@ -3240,7 +3513,7 @@
       <rgbColor rgb="FF6B7280"/>
       <rgbColor rgb="FFA5A5A5"/>
       <rgbColor rgb="FF17324D"/>
-      <rgbColor rgb="FF579D1C"/>
+      <rgbColor rgb="FF548235"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FFB42318"/>
@@ -3725,11 +3998,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="6215438"/>
-        <c:axId val="76554859"/>
+        <c:axId val="25580201"/>
+        <c:axId val="18065159"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6215438"/>
+        <c:axId val="25580201"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3757,7 +4030,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76554859"/>
+        <c:crossAx val="18065159"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3765,7 +4038,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76554859"/>
+        <c:axId val="18065159"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3802,7 +4075,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6215438"/>
+        <c:crossAx val="25580201"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4038,11 +4311,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="87878130"/>
-        <c:axId val="67097203"/>
+        <c:axId val="1374937"/>
+        <c:axId val="10205624"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="87878130"/>
+        <c:axId val="1374937"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4070,7 +4343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67097203"/>
+        <c:crossAx val="10205624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4078,7 +4351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67097203"/>
+        <c:axId val="10205624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4115,7 +4388,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87878130"/>
+        <c:crossAx val="1374937"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4369,11 +4642,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="84166390"/>
-        <c:axId val="22379924"/>
+        <c:axId val="21107798"/>
+        <c:axId val="92504758"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84166390"/>
+        <c:axId val="21107798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4401,7 +4674,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22379924"/>
+        <c:crossAx val="92504758"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4409,7 +4682,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22379924"/>
+        <c:axId val="92504758"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4446,7 +4719,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84166390"/>
+        <c:crossAx val="21107798"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4655,11 +4928,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="28588920"/>
-        <c:axId val="76155161"/>
+        <c:axId val="89551413"/>
+        <c:axId val="53789986"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="28588920"/>
+        <c:axId val="89551413"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4687,12 +4960,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76155161"/>
+        <c:crossAx val="53789986"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="76155161"/>
+        <c:axId val="53789986"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4729,7 +5002,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28588920"/>
+        <c:crossAx val="89551413"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7578,6 +7851,924 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF548235"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="23.49"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="G5" s="121" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="B6" s="130" t="n">
+        <v>15840</v>
+      </c>
+      <c r="C6" s="130" t="n">
+        <v>15840</v>
+      </c>
+      <c r="D6" s="130" t="n">
+        <v>15840</v>
+      </c>
+      <c r="E6" s="130" t="n">
+        <v>15840</v>
+      </c>
+      <c r="F6" s="130" t="n">
+        <v>15840</v>
+      </c>
+      <c r="G6" s="124" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="92" t="n">
+        <v>68523840</v>
+      </c>
+      <c r="C7" s="92" t="n">
+        <v>70579555.2</v>
+      </c>
+      <c r="D7" s="92" t="n">
+        <v>72696941.856</v>
+      </c>
+      <c r="E7" s="92" t="n">
+        <v>74877850.11168</v>
+      </c>
+      <c r="F7" s="92" t="n">
+        <v>77124185.6150304</v>
+      </c>
+      <c r="G7" s="126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" s="90" t="n">
+        <v>-39699351.9648</v>
+      </c>
+      <c r="C8" s="90" t="n">
+        <v>-40890332.523744</v>
+      </c>
+      <c r="D8" s="90" t="n">
+        <v>-42117042.4994563</v>
+      </c>
+      <c r="E8" s="90" t="n">
+        <v>-43380553.77444</v>
+      </c>
+      <c r="F8" s="90" t="n">
+        <v>-44681970.3876732</v>
+      </c>
+      <c r="G8" s="124" t="n">
+        <v>-0.579350952380953</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="B9" s="92" t="n">
+        <v>28824488.0352</v>
+      </c>
+      <c r="C9" s="92" t="n">
+        <v>29689222.676256</v>
+      </c>
+      <c r="D9" s="92" t="n">
+        <v>30579899.3565437</v>
+      </c>
+      <c r="E9" s="92" t="n">
+        <v>31497296.33724</v>
+      </c>
+      <c r="F9" s="92" t="n">
+        <v>32442215.2273572</v>
+      </c>
+      <c r="G9" s="126" t="n">
+        <v>0.420649047619048</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="B10" s="90" t="n">
+        <v>-47382678</v>
+      </c>
+      <c r="C10" s="90" t="n">
+        <v>-48804158.34</v>
+      </c>
+      <c r="D10" s="90" t="n">
+        <v>-50268283.0902</v>
+      </c>
+      <c r="E10" s="90" t="n">
+        <v>-51776331.582906</v>
+      </c>
+      <c r="F10" s="90" t="n">
+        <v>-53329621.5303932</v>
+      </c>
+      <c r="G10" s="124" t="n">
+        <v>-0.691477272727273</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="B11" s="92" t="n">
+        <v>-18558189.9648</v>
+      </c>
+      <c r="C11" s="92" t="n">
+        <v>-19114935.663744</v>
+      </c>
+      <c r="D11" s="92" t="n">
+        <v>-19688383.7336563</v>
+      </c>
+      <c r="E11" s="92" t="n">
+        <v>-20279035.245666</v>
+      </c>
+      <c r="F11" s="92" t="n">
+        <v>-20887406.303036</v>
+      </c>
+      <c r="G11" s="126" t="n">
+        <v>-0.270828225108225</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="B12" s="90" t="n">
+        <v>-2718401.34325</v>
+      </c>
+      <c r="C12" s="90" t="n">
+        <v>-2718401.34325</v>
+      </c>
+      <c r="D12" s="90" t="n">
+        <v>-2718401.34325</v>
+      </c>
+      <c r="E12" s="90" t="n">
+        <v>-2718401.34325</v>
+      </c>
+      <c r="F12" s="90" t="n">
+        <v>-2718401.34325</v>
+      </c>
+      <c r="G12" s="124" t="n">
+        <v>-0.0396708845162501</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="92" t="n">
+        <v>-21276591.30805</v>
+      </c>
+      <c r="C13" s="92" t="n">
+        <v>-21833337.006994</v>
+      </c>
+      <c r="D13" s="92" t="n">
+        <v>-22406785.0769063</v>
+      </c>
+      <c r="E13" s="92" t="n">
+        <v>-22997436.588916</v>
+      </c>
+      <c r="F13" s="92" t="n">
+        <v>-23605807.646286</v>
+      </c>
+      <c r="G13" s="126" t="n">
+        <v>-0.310499109624475</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B14" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="93" t="s">
+        <v>508</v>
+      </c>
+      <c r="B16" s="95" t="n">
+        <v>-21276591.30805</v>
+      </c>
+      <c r="C16" s="95" t="n">
+        <v>-21833337.006994</v>
+      </c>
+      <c r="D16" s="95" t="n">
+        <v>-22406785.0769063</v>
+      </c>
+      <c r="E16" s="95" t="n">
+        <v>-22997436.588916</v>
+      </c>
+      <c r="F16" s="95" t="n">
+        <v>-23605807.646286</v>
+      </c>
+      <c r="G16" s="131" t="n">
+        <v>-0.310499109624475</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF548235"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="23.49"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="F5" s="121" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="B6" s="90" t="n">
+        <v>5632096.43835617</v>
+      </c>
+      <c r="C6" s="90" t="n">
+        <v>5801059.33150685</v>
+      </c>
+      <c r="D6" s="90" t="n">
+        <v>5975091.11145206</v>
+      </c>
+      <c r="E6" s="90" t="n">
+        <v>6154343.84479562</v>
+      </c>
+      <c r="F6" s="122" t="n">
+        <v>6338974.16013949</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="B7" s="92" t="n">
+        <v>1631480.21773151</v>
+      </c>
+      <c r="C7" s="92" t="n">
+        <v>1680424.62426345</v>
+      </c>
+      <c r="D7" s="92" t="n">
+        <v>1730837.36299136</v>
+      </c>
+      <c r="E7" s="92" t="n">
+        <v>1782762.4838811</v>
+      </c>
+      <c r="F7" s="132" t="n">
+        <v>1836245.35839753</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="B8" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="B9" s="92" t="n">
+        <v>7263576.65608767</v>
+      </c>
+      <c r="C9" s="92" t="n">
+        <v>7481483.9557703</v>
+      </c>
+      <c r="D9" s="92" t="n">
+        <v>7705928.47444341</v>
+      </c>
+      <c r="E9" s="92" t="n">
+        <v>7937106.32867671</v>
+      </c>
+      <c r="F9" s="132" t="n">
+        <v>8175219.51853702</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="93" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="95" t="n">
+        <v>217907.299682629</v>
+      </c>
+      <c r="D10" s="95" t="n">
+        <v>224444.51867311</v>
+      </c>
+      <c r="E10" s="95" t="n">
+        <v>231177.854233301</v>
+      </c>
+      <c r="F10" s="123" t="n">
+        <v>238113.189860302</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="101" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="103" t="s">
+        <v>517</v>
+      </c>
+      <c r="B14" s="133" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="105" t="s">
+        <v>518</v>
+      </c>
+      <c r="B15" s="134" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="105" t="s">
+        <v>519</v>
+      </c>
+      <c r="B16" s="134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="109" t="s">
+        <v>520</v>
+      </c>
+      <c r="B17" s="135" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="98" t="s">
+        <v>521</v>
+      </c>
+      <c r="B20" s="98"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A20:F20"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="66.4"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
+        <v>525</v>
+      </c>
+      <c r="B6" s="90" t="n">
+        <v>4326</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>527</v>
+      </c>
+      <c r="B7" s="92" t="n">
+        <v>2506.27222</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8" s="90" t="n">
+        <v>1819.72778</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>531</v>
+      </c>
+      <c r="B9" s="100" t="n">
+        <v>0.420649047619048</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
+        <v>533</v>
+      </c>
+      <c r="B10" s="90" t="n">
+        <v>3833550</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="B11" s="136" t="n">
+        <v>2169.86108768423</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>536</v>
+      </c>
+      <c r="B12" s="130" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="B13" s="100" t="n">
+        <v>1.64383415733653</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>539</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>542</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>540</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
+        <v>544</v>
+      </c>
+      <c r="B16" s="89" t="n">
+        <v>-0.731227795942604</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="102" t="n">
+        <v>-1.38553330647718</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>546</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>B13&gt;1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>B13&lt;=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF17324D"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="66.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="66.4"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>550</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="137" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>554</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>555</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>556</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="138" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>558</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>559</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>560</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="137" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>562</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>563</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>564</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="138" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>566</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>567</v>
+      </c>
+      <c r="D9" s="139" t="s">
+        <v>568</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="137" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>570</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>571</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="140" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>574</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>575</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>576</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>577</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFA5A5A5"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
@@ -7590,7 +8781,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>503</v>
+        <v>578</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7601,7 +8792,7 @@
     </row>
     <row r="2" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>504</v>
+        <v>579</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7612,79 +8803,79 @@
     </row>
     <row r="4" customFormat="false" ht="18.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="45" t="s">
-        <v>505</v>
+        <v>580</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>506</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="86" t="s">
-        <v>507</v>
+        <v>582</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>508</v>
+        <v>583</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="86" t="s">
-        <v>509</v>
+        <v>584</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>508</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="86" t="s">
-        <v>510</v>
+        <v>585</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>511</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="86" t="s">
-        <v>512</v>
+        <v>587</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>508</v>
+        <v>583</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="86" t="s">
-        <v>513</v>
+        <v>588</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>508</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="86" t="s">
-        <v>514</v>
+        <v>589</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>508</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="86" t="s">
-        <v>515</v>
+        <v>590</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>508</v>
+        <v>583</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="101" t="s">
-        <v>516</v>
+        <v>591</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="86" t="s">
-        <v>517</v>
-      </c>
-      <c r="B14" s="130" t="s">
-        <v>518</v>
+        <v>592</v>
+      </c>
+      <c r="B14" s="141" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7707,7 +8898,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="86" t="s">
-        <v>519</v>
+        <v>594</v>
       </c>
       <c r="B17" s="86" t="str">
         <f aca="false">IF(ISNA(Calculos!$B$48),"NO — flujo sin cambio de signo","sí")</f>
